--- a/rules/CORE-000538/negative/01/data/unit-test-coreid-CG0334-negative 1.xlsx
+++ b/rules/CORE-000538/negative/01/data/unit-test-coreid-CG0334-negative 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000538\negative\01\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian_try2\core-contributor\rules\CORE-000538\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95E4574-5CBB-40E1-8ECF-56D6D340A60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FBDD54-5EED-46E9-8CD7-2462C03F920C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
   <si>
     <t>Product</t>
   </si>
@@ -155,6 +155,15 @@
   </si>
   <si>
     <t>CLINICAL STUDY SPONSOR</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>$dataset_name</t>
+  </si>
+  <si>
+    <t>SUPPAE</t>
   </si>
 </sst>
 </file>
@@ -173,16 +182,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -199,6 +206,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -229,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -251,6 +264,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +623,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -628,6 +644,86 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -637,7 +733,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -772,7 +868,7 @@
       <c r="A5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -804,7 +900,7 @@
       <c r="A6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -829,262 +925,6 @@
         <v>42</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="6">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="8">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="6">
-        <v>13</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="8">
-        <v>14</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="6">
-        <v>15</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="6">
-        <v>3</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="8">
-        <v>4</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="7" t="s">
         <v>43</v>
       </c>
     </row>
